--- a/packages/calculators/src/modules/test/6.2-pasture-residues.xlsx
+++ b/packages/calculators/src/modules/test/6.2-pasture-residues.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB2E7BA-DCAD-274A-9855-2AB25038F3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA65D4C-80FE-3841-AD74-D3A7F64C7335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="620" windowWidth="28800" windowHeight="15900" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="17160" yWindow="-16020" windowWidth="28800" windowHeight="15900" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="6.2.1.1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t>Method 1</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>NOTE: Pending feedback, I think this formula is incorrect. Multiplying by 10^-3 converts the yield in tonnes to gigagrams, not kilograms. I've implemented this with what I think is the correct conversion</t>
+  </si>
+  <si>
+    <t>t DM / ha</t>
   </si>
 </sst>
 </file>
@@ -430,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -448,6 +451,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf applyFill="1" numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -842,7 +846,7 @@
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="13">
         <v>15</v>
       </c>
       <c r="E4" t="s">
@@ -881,37 +885,37 @@
         <v>5000</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:D10" si="0">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,2, FALSE)/ 1000)</f>
-        <v>4.4099999999999999E-3</v>
+        <f>IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,2, FALSE))</f>
+        <v>4.41</v>
       </c>
       <c r="E5" s="12">
-        <f t="shared" ref="E5:E10" si="1">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,6, FALSE))</f>
+        <f t="shared" ref="E5:E10" si="0">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,6, FALSE))</f>
         <v>0.8</v>
       </c>
       <c r="F5" s="12">
-        <f t="shared" ref="F5:F10" si="2">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,4, FALSE))</f>
+        <f t="shared" ref="F5:F10" si="1">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,4, FALSE))</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G5" s="12">
-        <f t="shared" ref="G5:G10" si="3">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,3, FALSE))</f>
+        <f t="shared" ref="G5:G10" si="2">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,3, FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" ref="H5:H10" si="4">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,5, FALSE))</f>
+        <f t="shared" ref="H5:H10" si="3">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,5, FALSE))</f>
         <v>1.2E-2</v>
       </c>
       <c r="I5" s="12"/>
       <c r="J5">
-        <f>IF(ISBLANK(A5),"", (C5*(D5 * 1000) *(1 - E5)*F5)+(C5*(D5 *1000)*G5*H5))</f>
-        <v>171.98999999999998</v>
+        <f>IF(ISBLANK(A5),"", (C5*(D5 * 10^-3) *(1 - E5)*F5)+(C5*(D5 *10^-3)*G5*H5))</f>
+        <v>0.17198999999999998</v>
       </c>
       <c r="K5">
         <f>IF(ISBLANK(A5),"",VLOOKUP(A5,$N$14:$O$15,2,FALSE))</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L5">
-        <f>IF(ISBLANK(A5), "", J5*K5*$O$10/1000)</f>
-        <v>1.6216199999999998E-3</v>
+        <f>IF(ISBLANK(A5), "", J5*K5*$O$10 * 10^3)</f>
+        <v>1.6216199999999998</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -925,37 +929,37 @@
         <v>50</v>
       </c>
       <c r="D6">
+        <f t="shared" ref="D6:D10" si="4">IF(ISBLANK(A6), "", VLOOKUP(B6, $N$20:$S$24,2, FALSE))</f>
+        <v>4.41</v>
+      </c>
+      <c r="E6" s="12">
         <f t="shared" si="0"/>
-        <v>4.4099999999999999E-3</v>
-      </c>
-      <c r="E6" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="F6" s="12">
         <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="F6" s="12">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G6" s="12">
         <f t="shared" si="2"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G6" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="H6" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
-      </c>
-      <c r="H6" s="12">
-        <f t="shared" si="4"/>
         <v>1.2E-2</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6">
-        <f t="shared" ref="J6:J20" si="5">IF(ISBLANK(A6),"", (C6*(D6 * 1000) *(1 - E6)*F6)+(C6*(D6 *1000)*G6*H6))</f>
-        <v>1.7198999999999998</v>
+        <f t="shared" ref="J6:J10" si="5">IF(ISBLANK(A6),"", (C6*(D6 * 10^-3) *(1 - E6)*F6)+(C6*(D6 *10^-3)*G6*H6))</f>
+        <v>1.7198999999999999E-3</v>
       </c>
       <c r="K6">
         <f t="shared" ref="K6" si="6">IF(ISBLANK(A6),"",VLOOKUP(A6,$N$14:$O$15,2,FALSE))</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L6">
-        <f t="shared" ref="L6:L10" si="7">IF(ISBLANK(A6), "", J6*K6*$O$10/1000)</f>
-        <v>1.35135E-5</v>
+        <f t="shared" ref="L6:L10" si="7">IF(ISBLANK(A6), "", J6*K6*$O$10 * 10^3)</f>
+        <v>1.3513499999999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -969,29 +973,29 @@
         <v>600</v>
       </c>
       <c r="D7">
+        <f t="shared" si="4"/>
+        <v>8.34</v>
+      </c>
+      <c r="E7" s="12">
         <f t="shared" si="0"/>
-        <v>8.3400000000000002E-3</v>
-      </c>
-      <c r="E7" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="12">
         <f t="shared" si="1"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G7" s="12">
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="F7" s="12">
-        <f t="shared" si="2"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="G7" s="12">
+      <c r="H7" s="12">
         <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="H7" s="12">
-        <f t="shared" si="4"/>
         <v>1.6E-2</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7">
         <f t="shared" si="5"/>
-        <v>89.071200000000005</v>
+        <v>8.9071200000000017E-2</v>
       </c>
       <c r="K7">
         <f>IF(ISBLANK(A7),"",VLOOKUP(A7,$N$14:$O$15,2,FALSE))</f>
@@ -999,7 +1003,7 @@
       </c>
       <c r="L7">
         <f t="shared" si="7"/>
-        <v>8.3981417142857135E-4</v>
+        <v>0.83981417142857162</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1013,29 +1017,29 @@
         <v>7000</v>
       </c>
       <c r="D8">
+        <f t="shared" si="4"/>
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="E8" s="12">
         <f t="shared" si="0"/>
-        <v>8.6199999999999992E-3</v>
-      </c>
-      <c r="E8" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="F8" s="12">
+        <v>2.7E-2</v>
+      </c>
+      <c r="G8" s="12">
         <f t="shared" si="2"/>
-        <v>2.7E-2</v>
-      </c>
-      <c r="G8" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="H8" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
-      </c>
-      <c r="H8" s="12">
-        <f t="shared" si="4"/>
         <v>1.9E-2</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8">
         <f t="shared" si="5"/>
-        <v>784.41999999999985</v>
+        <v>0.7844199999999999</v>
       </c>
       <c r="K8">
         <f>IF(ISBLANK(A8),"",VLOOKUP(A8,$N$14:$O$15,2,FALSE))</f>
@@ -1043,7 +1047,7 @@
       </c>
       <c r="L8">
         <f t="shared" si="7"/>
-        <v>6.1632999999999983E-3</v>
+        <v>6.1632999999999996</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1059,29 +1063,29 @@
         <v>50</v>
       </c>
       <c r="D9">
+        <f t="shared" si="4"/>
+        <v>5.62</v>
+      </c>
+      <c r="E9" s="12">
         <f t="shared" si="0"/>
-        <v>5.62E-3</v>
-      </c>
-      <c r="E9" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="F9" s="12">
+        <v>2.7E-2</v>
+      </c>
+      <c r="G9" s="12">
         <f t="shared" si="2"/>
-        <v>2.7E-2</v>
-      </c>
-      <c r="G9" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="H9" s="12">
         <f t="shared" si="3"/>
-        <v>0.4</v>
-      </c>
-      <c r="H9" s="12">
-        <f t="shared" si="4"/>
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9">
         <f t="shared" si="5"/>
-        <v>3.9901999999999997</v>
+        <v>3.9902000000000002E-3</v>
       </c>
       <c r="K9">
         <f>IF(ISBLANK(A9),"",VLOOKUP(A9,$N$14:$O$15,2,FALSE))</f>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="L9">
         <f t="shared" si="7"/>
-        <v>3.7621885714285712E-5</v>
+        <v>3.7621885714285715E-2</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1105,29 +1109,29 @@
         <v>50</v>
       </c>
       <c r="D10">
+        <f t="shared" si="4"/>
+        <v>8.35</v>
+      </c>
+      <c r="E10" s="12">
         <f t="shared" si="0"/>
-        <v>8.3499999999999998E-3</v>
-      </c>
-      <c r="E10" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="F10" s="12">
         <f t="shared" si="1"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="F10" s="12">
-        <f t="shared" si="2"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="G10" s="12">
+      <c r="H10" s="12">
         <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="H10" s="12">
-        <f t="shared" si="4"/>
         <v>1.2E-2</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10">
         <f t="shared" si="5"/>
-        <v>5.2604999999999995</v>
+        <v>5.2604999999999996E-3</v>
       </c>
       <c r="K10">
         <f>IF(ISBLANK(A10),"",VLOOKUP(A10,$N$14:$O$15,2,FALSE))</f>
@@ -1135,7 +1139,7 @@
       </c>
       <c r="L10">
         <f t="shared" si="7"/>
-        <v>4.1332500000000004E-5</v>
+        <v>4.1332499999999994E-2</v>
       </c>
       <c r="N10" t="s">
         <v>2</v>
@@ -1164,15 +1168,15 @@
       </c>
       <c r="I11" s="12"/>
       <c r="J11" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J6:J20" si="12">IF(ISBLANK(A11),"", (C11*(D11 * 1000) *(1 - E11)*F11)+(C11*(D11 *1000)*G11*H11))</f>
         <v/>
       </c>
       <c r="K11" t="str">
-        <f t="shared" ref="K11:K20" si="12">IF(ISBLANK(A11),"",VLOOKUP(A11,$N$14:$O$15,2,FALSE))</f>
+        <f t="shared" ref="K11:K20" si="13">IF(ISBLANK(A11),"",VLOOKUP(A11,$N$14:$O$15,2,FALSE))</f>
         <v/>
       </c>
       <c r="L11" t="str">
-        <f t="shared" ref="L11:L20" si="13">IF(ISBLANK(A11), "", J11*K11*$O$10/1000)</f>
+        <f t="shared" ref="L11:L20" si="14">IF(ISBLANK(A11), "", J11*K11*$O$10/1000)</f>
         <v/>
       </c>
       <c r="N11" s="2"/>
@@ -1202,15 +1206,15 @@
       </c>
       <c r="I12" s="12"/>
       <c r="J12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K12" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L12" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N12" s="2" t="s">
@@ -1242,15 +1246,15 @@
       </c>
       <c r="I13" s="12"/>
       <c r="J13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K13" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L13" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N13" t="s">
@@ -1281,15 +1285,15 @@
       </c>
       <c r="I14" s="12"/>
       <c r="J14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N14" s="2" t="s">
@@ -1324,15 +1328,15 @@
       </c>
       <c r="I15" s="12"/>
       <c r="J15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N15" s="2" t="s">
@@ -1368,15 +1372,15 @@
       </c>
       <c r="I16" s="12"/>
       <c r="J16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K16" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L16" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N16" s="2"/>
@@ -1414,16 +1418,16 @@
       </c>
       <c r="I17" s="12"/>
       <c r="J17">
-        <f t="shared" si="5"/>
-        <v>195</v>
+        <f>IF(ISBLANK(A17),"", (C17*(D17 * 10^-3) *(1 - E17)*F17)+(C17*(D17 *10 ^ -3)*G17*H17))</f>
+        <v>1.9500000000000002E-4</v>
       </c>
       <c r="K17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L17">
-        <f t="shared" si="13"/>
-        <v>1.5321428571428571E-3</v>
+        <f>IF(ISBLANK(A17), "", J17*K17*$O$10 * 10^3)</f>
+        <v>1.5321428571428574E-3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1457,19 +1461,21 @@
       </c>
       <c r="I18" s="12"/>
       <c r="J18">
-        <f t="shared" si="5"/>
-        <v>10680</v>
+        <f t="shared" ref="J18:J20" si="15">IF(ISBLANK(A18),"", (C18*(D18 * 10^-3) *(1 - E18)*F18)+(C18*(D18 *10 ^ -3)*G18*H18))</f>
+        <v>1.0679999999999999E-2</v>
       </c>
       <c r="K18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L18">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="L18:L20" si="16">IF(ISBLANK(A18), "", J18*K18*$O$10 * 10^3)</f>
         <v>0.10069714285714285</v>
       </c>
       <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+      <c r="O18" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="19" spans="1:22" ht="17">
       <c r="A19" t="s">
@@ -1502,16 +1508,16 @@
       </c>
       <c r="I19" s="12"/>
       <c r="J19">
-        <f t="shared" si="5"/>
-        <v>909999.99999999988</v>
+        <f t="shared" si="15"/>
+        <v>0.90999999999999992</v>
       </c>
       <c r="K19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L19">
-        <f t="shared" si="13"/>
-        <v>7.1499999999999986</v>
+        <f t="shared" si="16"/>
+        <v>7.1499999999999995</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>18</v>
@@ -1563,16 +1569,16 @@
       </c>
       <c r="I20" s="12"/>
       <c r="J20">
-        <f t="shared" si="5"/>
-        <v>8875</v>
+        <f t="shared" si="15"/>
+        <v>8.8749999999999992E-3</v>
       </c>
       <c r="K20">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L20">
-        <f t="shared" si="13"/>
-        <v>8.3678571428571435E-2</v>
+        <f t="shared" si="16"/>
+        <v>8.3678571428571422E-2</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>25</v>

--- a/packages/calculators/src/modules/test/6.2-pasture-residues.xlsx
+++ b/packages/calculators/src/modules/test/6.2-pasture-residues.xlsx
@@ -1,20 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA65D4C-80FE-3841-AD74-D3A7F64C7335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F0EB12-C400-6747-BD28-AB540E0B8D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17160" yWindow="-16020" windowWidth="28800" windowHeight="15900" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="6.2.1.1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -433,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -451,7 +449,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf applyFill="1" numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,6 +464,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -846,7 +865,7 @@
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s" s="13">
+      <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E4" t="s">
@@ -915,7 +934,7 @@
       </c>
       <c r="L5">
         <f>IF(ISBLANK(A5), "", J5*K5*$O$10 * 10^3)</f>
-        <v>1.6216199999999998</v>
+        <v>1.6201457999999997</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -959,7 +978,7 @@
       </c>
       <c r="L6">
         <f t="shared" ref="L6:L10" si="7">IF(ISBLANK(A6), "", J6*K6*$O$10 * 10^3)</f>
-        <v>1.3513499999999998E-2</v>
+        <v>1.3501215E-2</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1003,7 +1022,7 @@
       </c>
       <c r="L7">
         <f t="shared" si="7"/>
-        <v>0.83981417142857162</v>
+        <v>0.83905070400000026</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1047,7 +1066,7 @@
       </c>
       <c r="L8">
         <f t="shared" si="7"/>
-        <v>6.1632999999999996</v>
+        <v>6.1576969999999989</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1093,7 +1112,7 @@
       </c>
       <c r="L9">
         <f t="shared" si="7"/>
-        <v>3.7621885714285715E-2</v>
+        <v>3.7587684000000003E-2</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1139,14 +1158,14 @@
       </c>
       <c r="L10">
         <f t="shared" si="7"/>
-        <v>4.1332499999999994E-2</v>
+        <v>4.1294924999999996E-2</v>
       </c>
       <c r="N10" t="s">
         <v>2</v>
       </c>
       <c r="O10">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1168,7 +1187,7 @@
       </c>
       <c r="I11" s="12"/>
       <c r="J11" t="str">
-        <f t="shared" ref="J6:J20" si="12">IF(ISBLANK(A11),"", (C11*(D11 * 1000) *(1 - E11)*F11)+(C11*(D11 *1000)*G11*H11))</f>
+        <f t="shared" ref="J11:J16" si="12">IF(ISBLANK(A11),"", (C11*(D11 * 1000) *(1 - E11)*F11)+(C11*(D11 *1000)*G11*H11))</f>
         <v/>
       </c>
       <c r="K11" t="str">
@@ -1176,7 +1195,7 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <f t="shared" ref="L11:L20" si="14">IF(ISBLANK(A11), "", J11*K11*$O$10/1000)</f>
+        <f t="shared" ref="L11:L16" si="14">IF(ISBLANK(A11), "", J11*K11*$O$10/1000)</f>
         <v/>
       </c>
       <c r="N11" s="2"/>
@@ -1427,7 +1446,7 @@
       </c>
       <c r="L17">
         <f>IF(ISBLANK(A17), "", J17*K17*$O$10 * 10^3)</f>
-        <v>1.5321428571428574E-3</v>
+        <v>1.5307500000000004E-3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1470,7 +1489,7 @@
       </c>
       <c r="L18">
         <f t="shared" ref="L18:L20" si="16">IF(ISBLANK(A18), "", J18*K18*$O$10 * 10^3)</f>
-        <v>0.10069714285714285</v>
+        <v>0.1006056</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
@@ -1517,7 +1536,7 @@
       </c>
       <c r="L19">
         <f t="shared" si="16"/>
-        <v>7.1499999999999995</v>
+        <v>7.1434999999999995</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>18</v>
@@ -1578,7 +1597,7 @@
       </c>
       <c r="L20">
         <f t="shared" si="16"/>
-        <v>8.3678571428571422E-2</v>
+        <v>8.3602499999999996E-2</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>25</v>
